--- a/reports/LeetCode_Daily_Report_2026-08-24.xlsx
+++ b/reports/LeetCode_Daily_Report_2026-08-24.xlsx
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31">

--- a/reports/LeetCode_Daily_Report_2026-08-24.xlsx
+++ b/reports/LeetCode_Daily_Report_2026-08-24.xlsx
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31">

--- a/reports/LeetCode_Daily_Report_2026-08-24.xlsx
+++ b/reports/LeetCode_Daily_Report_2026-08-24.xlsx
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46">
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47">

--- a/reports/LeetCode_Daily_Report_2026-08-24.xlsx
+++ b/reports/LeetCode_Daily_Report_2026-08-24.xlsx
@@ -1455,15 +1455,11 @@
           <t>24-Aug-2026</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="43">
@@ -2068,7 +2064,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>No usable profile URL in master file</t>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
         </is>
       </c>
     </row>

--- a/reports/LeetCode_Daily_Report_2026-08-24.xlsx
+++ b/reports/LeetCode_Daily_Report_2026-08-24.xlsx
@@ -1211,15 +1211,11 @@
           <t>24-Aug-2026</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="33">
@@ -1968,7 +1964,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>No usable profile URL in master file</t>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
         </is>
       </c>
     </row>
